--- a/Excel/PlayerModel.xlsx
+++ b/Excel/PlayerModel.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -83,7 +83,7 @@
     <t>战神</t>
   </si>
   <si>
-    <t>11004,11007</t>
+    <t>1004,1007</t>
   </si>
   <si>
     <t>烈火</t>
@@ -116,13 +116,13 @@
     <t>召唤</t>
   </si>
   <si>
-    <t>3004,13002</t>
+    <t>3004,3002</t>
   </si>
   <si>
     <t>火神</t>
   </si>
   <si>
-    <t>12001,12003</t>
+    <t>2001,2003</t>
   </si>
   <si>
     <t>战五渣</t>
@@ -131,112 +131,7 @@
     <t>啥都不会</t>
   </si>
   <si>
-    <t>皇级</t>
-  </si>
-  <si>
-    <t>1001,1002,2001</t>
-  </si>
-  <si>
-    <t>2001,2007,1007</t>
-  </si>
-  <si>
-    <t>3002,3007,1009</t>
-  </si>
-  <si>
-    <t>1002,2003,2002</t>
-  </si>
-  <si>
-    <t>3003,2002,1007</t>
-  </si>
-  <si>
-    <t>2001,1002,1009</t>
-  </si>
-  <si>
-    <t>2001,2003,2004</t>
-  </si>
-  <si>
-    <t>1009,2001,2003</t>
-  </si>
-  <si>
-    <t>1002,1009,2003</t>
-  </si>
-  <si>
-    <t>2002,2007,2009</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,2007,2008</t>
-  </si>
-  <si>
-    <t>1001,1002,1007,1008</t>
-  </si>
-  <si>
-    <t>天级</t>
-  </si>
-  <si>
-    <t>2002,2003,2007,2008,2009,2010</t>
-  </si>
-  <si>
-    <t>1001,1002,1004,1007,1008,1010</t>
-  </si>
-  <si>
-    <t>1002,2002,1004,2007,1010,2010</t>
-  </si>
-  <si>
-    <t>神级</t>
-  </si>
-  <si>
-    <t>2002,2003,2007,2008,2009,2012</t>
-  </si>
-  <si>
-    <t>1004,1007,1008,1010,1012</t>
-  </si>
-  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>3002,3001,2007,3012,1008</t>
-  </si>
-  <si>
-    <t>王级</t>
-  </si>
-  <si>
-    <t>3001,3003</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>1001,1002,1003</t>
-  </si>
-  <si>
-    <t>2001,2002,2003</t>
-  </si>
-  <si>
-    <t>地级</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1007</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,2004</t>
-  </si>
-  <si>
-    <t>3001,3002,3003</t>
-  </si>
-  <si>
-    <t>君级</t>
-  </si>
-  <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>将级</t>
   </si>
 </sst>
 </file>
@@ -883,12 +778,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1387,7 +1281,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="3:13">
+    <row r="6" ht="24" customHeight="1" spans="1:17">
       <c r="C6" s="3">
         <v>1</v>
       </c>
@@ -1406,7 +1300,7 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3">
-        <v>11002</v>
+        <v>1002</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -1416,7 +1310,7 @@
       </c>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="3:13">
+    <row r="7" ht="24" customHeight="1" spans="1:17">
       <c r="C7" s="3">
         <v>2</v>
       </c>
@@ -1445,7 +1339,7 @@
       </c>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="3:13">
+    <row r="8" ht="24" customHeight="1" spans="1:17">
       <c r="C8" s="3">
         <v>3</v>
       </c>
@@ -1464,7 +1358,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3">
-        <v>11007</v>
+        <v>1007</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -1474,7 +1368,7 @@
       </c>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="3:13">
+    <row r="9" ht="24" customHeight="1" spans="1:17">
       <c r="C9" s="3">
         <v>4</v>
       </c>
@@ -1493,7 +1387,7 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3">
-        <v>12001</v>
+        <v>2001</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -1503,7 +1397,7 @@
       </c>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="3:13">
+    <row r="10" ht="24" customHeight="1" spans="1:17">
       <c r="C10" s="3">
         <v>5</v>
       </c>
@@ -1522,7 +1416,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3">
-        <v>12002</v>
+        <v>2002</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -1532,7 +1426,7 @@
       </c>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="3:13">
+    <row r="11" ht="24" customHeight="1" spans="1:17">
       <c r="C11" s="3">
         <v>6</v>
       </c>
@@ -1551,7 +1445,7 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3">
-        <v>12003</v>
+        <v>2003</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -1561,7 +1455,7 @@
       </c>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="3:13">
+    <row r="12" ht="24" customHeight="1" spans="1:17">
       <c r="C12" s="3">
         <v>7</v>
       </c>
@@ -1580,7 +1474,7 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3">
-        <v>12004</v>
+        <v>2004</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -1590,7 +1484,7 @@
       </c>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="3:13">
+    <row r="13" ht="24" customHeight="1" spans="1:17">
       <c r="C13" s="3">
         <v>8</v>
       </c>
@@ -1609,7 +1503,7 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3">
-        <v>12007</v>
+        <v>2007</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -1619,7 +1513,7 @@
       </c>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="3:13">
+    <row r="14" ht="24" customHeight="1" spans="1:17">
       <c r="C14" s="3">
         <v>9</v>
       </c>
@@ -1638,7 +1532,7 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3">
-        <v>13001</v>
+        <v>3001</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1648,7 +1542,7 @@
       </c>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="3:13">
+    <row r="15" ht="24" customHeight="1" spans="1:17">
       <c r="C15" s="3">
         <v>10</v>
       </c>
@@ -1667,7 +1561,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3">
-        <v>13002</v>
+        <v>3002</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1677,7 +1571,7 @@
       </c>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" ht="24" customHeight="1" spans="3:13">
+    <row r="16" ht="24" customHeight="1" spans="1:17">
       <c r="C16" s="3">
         <v>11</v>
       </c>
@@ -1696,7 +1590,7 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3">
-        <v>13003</v>
+        <v>3003</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -1807,766 +1701,350 @@
       <c r="M20" s="3"/>
     </row>
     <row r="21" ht="24" customHeight="1" spans="3:13">
-      <c r="C21" s="3">
-        <v>3001</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1070</v>
-      </c>
-      <c r="G21" s="3">
-        <v>5</v>
-      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-      <c r="J21" s="3">
-        <v>1001</v>
-      </c>
-      <c r="K21" s="3">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3">
-        <v>4</v>
-      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="3:13">
-      <c r="C22" s="3">
-        <v>3002</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1071</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1071</v>
-      </c>
-      <c r="G22" s="3">
-        <v>5</v>
-      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="3">
-        <v>2001</v>
-      </c>
-      <c r="K22" s="3">
-        <v>4</v>
-      </c>
-      <c r="L22" s="3">
-        <v>4</v>
-      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
     <row r="23" ht="24" customHeight="1" spans="3:13">
-      <c r="C23" s="3">
-        <v>3003</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1072</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1072</v>
-      </c>
-      <c r="G23" s="3">
-        <v>5</v>
-      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="3">
-        <v>3002</v>
-      </c>
-      <c r="K23" s="3">
-        <v>4</v>
-      </c>
-      <c r="L23" s="3">
-        <v>4</v>
-      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
       <c r="M23" s="3"/>
     </row>
     <row r="24" ht="24" customHeight="1" spans="3:13">
-      <c r="C24" s="3">
-        <v>3004</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="3">
-        <v>1073</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1073</v>
-      </c>
-      <c r="G24" s="3">
-        <v>5</v>
-      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="3">
-        <v>2002</v>
-      </c>
-      <c r="K24" s="3">
-        <v>4</v>
-      </c>
-      <c r="L24" s="3">
-        <v>4</v>
-      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
       <c r="M24" s="3"/>
     </row>
     <row r="25" ht="24" customHeight="1" spans="3:13">
-      <c r="C25" s="3">
-        <v>3005</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="3">
-        <v>1074</v>
-      </c>
-      <c r="F25" s="3">
-        <v>1074</v>
-      </c>
-      <c r="G25" s="3">
-        <v>5</v>
-      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="3">
-        <v>1002</v>
-      </c>
-      <c r="K25" s="3">
-        <v>4</v>
-      </c>
-      <c r="L25" s="3">
-        <v>4</v>
-      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
     <row r="26" ht="24" customHeight="1" spans="3:13">
-      <c r="C26" s="3">
-        <v>3006</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="3">
-        <v>1075</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1075</v>
-      </c>
-      <c r="G26" s="3">
-        <v>5</v>
-      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="K26" s="3">
-        <v>4</v>
-      </c>
-      <c r="L26" s="3">
-        <v>4</v>
-      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
     <row r="27" ht="24" customHeight="1" spans="3:13">
-      <c r="C27" s="3">
-        <v>3007</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1076</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1076</v>
-      </c>
-      <c r="G27" s="3">
-        <v>5</v>
-      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K27" s="3">
-        <v>4</v>
-      </c>
-      <c r="L27" s="3">
-        <v>4</v>
-      </c>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
     <row r="28" ht="24" customHeight="1" spans="3:13">
-      <c r="C28" s="3">
-        <v>3008</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="3">
-        <v>1077</v>
-      </c>
-      <c r="F28" s="3">
-        <v>1077</v>
-      </c>
-      <c r="G28" s="3">
-        <v>5</v>
-      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="K28" s="3">
-        <v>4</v>
-      </c>
-      <c r="L28" s="3">
-        <v>4</v>
-      </c>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
     <row r="29" ht="24" customHeight="1" spans="3:13">
-      <c r="C29" s="3">
-        <v>3009</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E29" s="3">
-        <v>1078</v>
-      </c>
-      <c r="F29" s="3">
-        <v>1078</v>
-      </c>
-      <c r="G29" s="3">
-        <v>5</v>
-      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K29" s="3">
-        <v>4</v>
-      </c>
-      <c r="L29" s="3">
-        <v>4</v>
-      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
     <row r="30" ht="24" customHeight="1" spans="3:13">
-      <c r="C30" s="3">
-        <v>3010</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" s="3">
-        <v>1079</v>
-      </c>
-      <c r="F30" s="3">
-        <v>1079</v>
-      </c>
-      <c r="G30" s="3">
-        <v>5</v>
-      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-      <c r="J30" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="K30" s="3">
-        <v>4</v>
-      </c>
-      <c r="L30" s="3">
-        <v>4</v>
-      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
     <row r="31" ht="24" customHeight="1" spans="3:13">
-      <c r="C31" s="3">
-        <v>3011</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="3">
-        <v>1080</v>
-      </c>
-      <c r="F31" s="3">
-        <v>1080</v>
-      </c>
-      <c r="G31" s="3">
-        <v>5</v>
-      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-      <c r="J31" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K31" s="3">
-        <v>4</v>
-      </c>
-      <c r="L31" s="3">
-        <v>4</v>
-      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
     <row r="32" ht="24" customHeight="1" spans="3:13">
-      <c r="C32" s="3">
-        <v>3012</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1081</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1081</v>
-      </c>
-      <c r="G32" s="3">
-        <v>5</v>
-      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K32" s="3">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3">
-        <v>4</v>
-      </c>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" ht="24" customHeight="1" spans="3:13">
-      <c r="C33" s="3">
-        <v>3013</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="3">
-        <v>1082</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1082</v>
-      </c>
-      <c r="G33" s="3">
-        <v>5</v>
-      </c>
+    <row r="33" ht="24" customHeight="1" spans="1:13">
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="K33" s="3">
-        <v>4</v>
-      </c>
-      <c r="L33" s="3">
-        <v>4</v>
-      </c>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" ht="24" customHeight="1" spans="3:13">
-      <c r="C34" s="3">
-        <v>3014</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="3">
-        <v>1083</v>
-      </c>
-      <c r="F34" s="3">
-        <v>1083</v>
-      </c>
-      <c r="G34" s="3">
-        <v>5</v>
-      </c>
+    <row r="34" ht="24" customHeight="1" spans="1:13">
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K34" s="3">
-        <v>4</v>
-      </c>
-      <c r="L34" s="3">
-        <v>4</v>
-      </c>
+      <c r="J34" s="6"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" ht="24" customHeight="1" spans="3:13">
-      <c r="C35" s="3">
-        <v>3015</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="3">
-        <v>1084</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1084</v>
-      </c>
-      <c r="G35" s="3">
-        <v>5</v>
-      </c>
+    <row r="35" ht="24" customHeight="1" spans="1:13">
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="K35" s="3">
-        <v>4</v>
-      </c>
-      <c r="L35" s="3">
-        <v>4</v>
-      </c>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" ht="24" customHeight="1" spans="3:13">
-      <c r="C36" s="3">
-        <v>3016</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E36" s="3">
-        <v>1085</v>
-      </c>
-      <c r="F36" s="5">
-        <v>1104</v>
-      </c>
-      <c r="G36" s="3">
-        <v>5</v>
-      </c>
+    <row r="36" ht="24" customHeight="1" spans="1:13">
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="K36" s="3">
-        <v>4</v>
-      </c>
-      <c r="L36" s="3">
-        <v>4</v>
-      </c>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" ht="24" customHeight="1" spans="3:13">
-      <c r="C37" s="3">
-        <v>3017</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="3">
-        <v>1085</v>
-      </c>
-      <c r="F37" s="5">
-        <v>1104</v>
-      </c>
-      <c r="G37" s="3">
-        <v>5</v>
-      </c>
+    <row r="37" ht="24" customHeight="1" spans="1:13">
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="K37" s="3">
-        <v>4</v>
-      </c>
-      <c r="L37" s="3">
-        <v>4</v>
-      </c>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" ht="24" customHeight="1" spans="3:13">
-      <c r="C38" s="3">
-        <v>3018</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="5">
-        <v>1105</v>
-      </c>
-      <c r="F38" s="3">
-        <v>1139</v>
-      </c>
-      <c r="G38" s="3">
-        <v>5</v>
-      </c>
+    <row r="38" ht="24" customHeight="1" spans="1:13">
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K38" s="3">
-        <v>5</v>
-      </c>
-      <c r="L38" s="3">
-        <v>5</v>
-      </c>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" ht="24" customHeight="1" spans="3:13">
-      <c r="C39" s="3">
-        <v>3019</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E39" s="5">
-        <v>1105</v>
-      </c>
-      <c r="F39" s="3">
-        <v>1139</v>
-      </c>
-      <c r="G39" s="3">
-        <v>5</v>
-      </c>
+    <row r="39" ht="24" customHeight="1" spans="1:13">
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K39" s="3">
-        <v>5</v>
-      </c>
-      <c r="L39" s="3">
-        <v>5</v>
-      </c>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" ht="24" customHeight="1" spans="3:13">
-      <c r="C40" s="3">
-        <v>3020</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" s="5">
-        <v>1105</v>
-      </c>
-      <c r="F40" s="3">
-        <v>1139</v>
-      </c>
-      <c r="G40" s="3">
-        <v>5</v>
-      </c>
+    <row r="40" ht="24" customHeight="1" spans="1:13">
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K40" s="3">
-        <v>5</v>
-      </c>
-      <c r="L40" s="3">
-        <v>5</v>
-      </c>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" ht="24" customHeight="1" spans="3:13">
-      <c r="C41" s="3">
-        <v>3021</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E41" s="5">
-        <v>1140</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G41" s="3">
-        <v>5</v>
-      </c>
+    <row r="41" ht="24" customHeight="1" spans="1:13">
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K41" s="3">
-        <v>10</v>
-      </c>
-      <c r="L41" s="3">
-        <v>10</v>
-      </c>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" ht="24" customHeight="1" spans="3:13">
-      <c r="C42" s="3">
-        <v>3022</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" s="5">
-        <v>1140</v>
-      </c>
-      <c r="F42" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G42" s="3">
-        <v>5</v>
-      </c>
+    <row r="42" ht="24" customHeight="1" spans="1:13">
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K42" s="3">
-        <v>10</v>
-      </c>
-      <c r="L42" s="3">
-        <v>10</v>
-      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" ht="24" customHeight="1" spans="3:13">
-      <c r="C43" s="3">
-        <v>3023</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E43" s="5">
-        <v>1140</v>
-      </c>
-      <c r="F43" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G43" s="3">
-        <v>5</v>
-      </c>
+    <row r="43" ht="24" customHeight="1" spans="1:13">
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K43" s="3">
-        <v>10</v>
-      </c>
-      <c r="L43" s="3">
-        <v>10</v>
-      </c>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" ht="24" customHeight="1" spans="3:13">
-      <c r="C44" s="3">
-        <v>3024</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" s="5">
-        <v>1176</v>
-      </c>
-      <c r="F44" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G44" s="3">
-        <v>5</v>
-      </c>
+    <row r="44" ht="24" customHeight="1" spans="1:13">
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="K44" s="3">
-        <v>15</v>
-      </c>
-      <c r="L44" s="3">
-        <v>15</v>
-      </c>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" ht="24" customHeight="1" spans="3:13">
-      <c r="C45" s="3">
-        <v>3025</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" s="5">
-        <v>1176</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>5</v>
-      </c>
+    <row r="45" ht="24" customHeight="1" spans="1:13">
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K45" s="3">
-        <v>15</v>
-      </c>
-      <c r="L45" s="3">
-        <v>15</v>
-      </c>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:13">
       <c r="A46" s="2" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="3">
-        <v>3026</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E46" s="5">
-        <v>1176</v>
-      </c>
-      <c r="F46" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G46" s="3">
-        <v>5</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="K46" s="3">
-        <v>15</v>
-      </c>
-      <c r="L46" s="3">
-        <v>15</v>
-      </c>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" ht="24" customHeight="1" spans="3:13">
+    <row r="47" ht="24" customHeight="1" spans="1:13">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -2579,7 +2057,7 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" ht="24" customHeight="1" spans="3:13">
+    <row r="48" ht="24" customHeight="1" spans="1:13">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -2606,322 +2084,146 @@
       <c r="M49" s="3"/>
     </row>
     <row r="50" ht="24" customHeight="1" spans="3:13">
-      <c r="C50" s="3">
-        <v>3101</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E50" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F50" s="3">
-        <v>1084</v>
-      </c>
-      <c r="G50" s="3">
-        <v>4</v>
-      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K50" s="3">
-        <v>3</v>
-      </c>
-      <c r="L50" s="3">
-        <v>1</v>
-      </c>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
     <row r="51" ht="24" customHeight="1" spans="3:13">
-      <c r="C51" s="3">
-        <v>3102</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E51" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F51" s="3">
-        <v>1084</v>
-      </c>
-      <c r="G51" s="3">
-        <v>4</v>
-      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
-      <c r="J51" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="K51" s="3">
-        <v>3</v>
-      </c>
-      <c r="L51" s="3">
-        <v>1</v>
-      </c>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
     <row r="52" ht="24" customHeight="1" spans="3:13">
-      <c r="C52" s="3">
-        <v>3103</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1084</v>
-      </c>
-      <c r="G52" s="3">
-        <v>4</v>
-      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
-      <c r="J52" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="K52" s="3">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1</v>
-      </c>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
       <c r="M52" s="3"/>
     </row>
     <row r="53" ht="24" customHeight="1" spans="3:13">
-      <c r="C53" s="3">
-        <v>3104</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E53" s="3">
-        <v>1085</v>
-      </c>
-      <c r="F53" s="5">
-        <v>1104</v>
-      </c>
-      <c r="G53" s="3">
-        <v>4</v>
-      </c>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
-      <c r="J53" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="K53" s="3">
-        <v>3</v>
-      </c>
-      <c r="L53" s="3">
-        <v>1</v>
-      </c>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
       <c r="M53" s="3"/>
     </row>
     <row r="54" ht="24" customHeight="1" spans="3:13">
-      <c r="C54" s="3">
-        <v>3105</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E54" s="3">
-        <v>1085</v>
-      </c>
-      <c r="F54" s="5">
-        <v>1104</v>
-      </c>
-      <c r="G54" s="3">
-        <v>4</v>
-      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
-      <c r="J54" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K54" s="3">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3">
-        <v>1</v>
-      </c>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
       <c r="M54" s="3"/>
     </row>
     <row r="55" ht="24" customHeight="1" spans="3:13">
-      <c r="C55" s="3">
-        <v>3106</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55" s="5">
-        <v>1105</v>
-      </c>
-      <c r="F55" s="3">
-        <v>1139</v>
-      </c>
-      <c r="G55" s="3">
-        <v>4</v>
-      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
-      <c r="J55" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="K55" s="3">
-        <v>4</v>
-      </c>
-      <c r="L55" s="3">
-        <v>2</v>
-      </c>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
     <row r="56" ht="24" customHeight="1" spans="3:13">
-      <c r="C56" s="3">
-        <v>3107</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E56" s="5">
-        <v>1105</v>
-      </c>
-      <c r="F56" s="3">
-        <v>1139</v>
-      </c>
-      <c r="G56" s="3">
-        <v>4</v>
-      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
-      <c r="J56" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K56" s="3">
-        <v>4</v>
-      </c>
-      <c r="L56" s="3">
-        <v>2</v>
-      </c>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
     <row r="57" ht="24" customHeight="1" spans="3:13">
-      <c r="C57" s="3">
-        <v>3108</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E57" s="5">
-        <v>1105</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1139</v>
-      </c>
-      <c r="G57" s="3">
-        <v>4</v>
-      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
-      <c r="J57" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="K57" s="3">
-        <v>4</v>
-      </c>
-      <c r="L57" s="3">
-        <v>2</v>
-      </c>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
     <row r="58" ht="24" customHeight="1" spans="3:13">
-      <c r="C58" s="3">
-        <v>3109</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E58" s="5">
-        <v>1140</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G58" s="3">
-        <v>4</v>
-      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
-      <c r="J58" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="K58" s="3">
-        <v>8</v>
-      </c>
-      <c r="L58" s="3">
-        <v>4</v>
-      </c>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
       <c r="M58" s="3"/>
     </row>
     <row r="59" ht="24" customHeight="1" spans="3:13">
-      <c r="C59" s="3">
-        <v>3110</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E59" s="5">
-        <v>1140</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G59" s="3">
-        <v>4</v>
-      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
-      <c r="J59" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K59" s="3">
-        <v>8</v>
-      </c>
-      <c r="L59" s="3">
-        <v>4</v>
-      </c>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
     <row r="60" ht="24" customHeight="1" spans="3:13">
-      <c r="C60" s="3">
-        <v>3111</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E60" s="5">
-        <v>1140</v>
-      </c>
-      <c r="F60" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G60" s="3">
-        <v>4</v>
-      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
-      <c r="J60" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="K60" s="3">
-        <v>8</v>
-      </c>
-      <c r="L60" s="3">
-        <v>4</v>
-      </c>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
     <row r="61" ht="24" customHeight="1" spans="3:13">
@@ -2938,90 +2240,42 @@
       <c r="M61" s="3"/>
     </row>
     <row r="62" ht="22" customHeight="1" spans="3:13">
-      <c r="C62" s="3">
-        <v>3201</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3</v>
-      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
-      <c r="J62" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K62" s="3">
-        <v>2</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
     <row r="63" ht="22" customHeight="1" spans="3:13">
-      <c r="C63" s="3">
-        <v>3202</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E63" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F63" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G63" s="3">
-        <v>3</v>
-      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
-      <c r="J63" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="K63" s="3">
-        <v>2</v>
-      </c>
-      <c r="L63" s="3">
-        <v>0</v>
-      </c>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
       <c r="M63" s="3"/>
     </row>
     <row r="64" ht="22" customHeight="1" spans="3:13">
-      <c r="C64" s="3">
-        <v>3203</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E64" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F64" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G64" s="3">
-        <v>3</v>
-      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
-      <c r="J64" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K64" s="3">
-        <v>2</v>
-      </c>
-      <c r="L64" s="3">
-        <v>0</v>
-      </c>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
       <c r="M64" s="3"/>
     </row>
     <row r="65" ht="24" customHeight="1" spans="3:13">
@@ -3038,32 +2292,16 @@
       <c r="M65" s="3"/>
     </row>
     <row r="66" ht="22" customHeight="1" spans="3:13">
-      <c r="C66" s="3">
-        <v>3301</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1105</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G66" s="3">
-        <v>2</v>
-      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
-      <c r="J66" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="K66" s="3">
-        <v>0</v>
-      </c>
-      <c r="L66" s="3">
-        <v>0</v>
-      </c>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
       <c r="M66" s="3"/>
     </row>
     <row r="67" ht="24" customHeight="1" spans="3:13">
